--- a/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
@@ -189,10 +189,10 @@
     <t>{nights}</t>
   </si>
   <si>
-    <t>{organization.costPerDay}</t>
+    <t>{costPerDayFormatted}</t>
   </si>
   <si>
-    <t>{totalPrice}</t>
+    <t>{totalCost}</t>
   </si>
   <si>
     <t xml:space="preserve">без НДС</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">Всего по счету:  ({totalPriceWords})  тенге 00 тиын</t>
+    <t xml:space="preserve">Всего по счету:  ({totalCostRu})  тенге 00 тиын</t>
   </si>
   <si>
     <t xml:space="preserve">Руководитель: Рыспаева Г.С.</t>
@@ -232,7 +232,6 @@
   <fonts count="8">
     <font>
       <sz val="8.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -299,20 +298,20 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -320,36 +319,36 @@
       <left style="none"/>
       <right style="none"/>
       <top style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -357,81 +356,81 @@
       <left style="none"/>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -440,7 +439,7 @@
       <left style="none"/>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -448,143 +447,143 @@
     <border>
       <left style="none"/>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -592,66 +591,66 @@
       <left style="none"/>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>

--- a/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
@@ -86,7 +86,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>{organization.organization}</t>
+      <t>{customer.organization.organization}</t>
     </r>
   </si>
   <si>
@@ -105,7 +105,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve"> Республика Казахстан, {organization.index}, город {organization.city}, {organization.address}</t>
+      <t xml:space="preserve"> Республика Казахстан, {customer.organization.index}, город {customer.organization.city}, {customer.organization.address}</t>
     </r>
   </si>
   <si>
@@ -124,7 +124,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">БИН {organization.bin}, {organization.bank}, БИК {organization.bik}</t>
+      <t xml:space="preserve">БИН {customer.organization.bin}, {customer.organization.bank}, БИК {customer.organization.bik}</t>
     </r>
   </si>
   <si>
@@ -143,7 +143,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve"> IBAN {organization.iik} </t>
+      <t xml:space="preserve"> IBAN {customer.organization.iik} </t>
     </r>
   </si>
   <si>

--- a/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
@@ -105,7 +105,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve"> Республика Казахстан, {customer.organization.index}, город {customer.organization.city}, {customer.organization.address}</t>
+      <t xml:space="preserve"> Республика Казахстан, {customer.organization.index} город {customer.organization.city}, {customer.organization.address}</t>
     </r>
   </si>
   <si>

--- a/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
@@ -1448,7 +1448,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr defaultColWidth="16.829999999999998" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -14560,8 +14560,8 @@
     <mergeCell ref="H34:K34"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="76" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
@@ -97,7 +97,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">БИН и адрес места нахождения получателя:</t>
+      <t xml:space="preserve">БИН и адрес места нахождения грузополучателя:</t>
     </r>
     <r>
       <rPr>
@@ -116,7 +116,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">БИН и адрес места нахождения получателя: </t>
+      <t xml:space="preserve">БИН и Банк грузополучателя: </t>
     </r>
     <r>
       <rPr>

--- a/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">Всего по счету:  ({totalCostRu})  тенге 00 тиын</t>
+    <t xml:space="preserve">Всего по счету:  ({totalCostRu})  тенге{totalCostCentsRu} тиын</t>
   </si>
   <si>
     <t xml:space="preserve">Руководитель: Рыспаева Г.С.</t>
